--- a/datasets/dataset2.xlsx
+++ b/datasets/dataset2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\userr\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1176B8-D681-419D-B7DA-DFB51F6FC342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED159D0-22AD-4434-81CF-990C96D1F017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5565" yWindow="2475" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1260,65 +1260,65 @@
     <t>Tayba</t>
   </si>
   <si>
-    <t>Name</t>
+    <t>dob</t>
   </si>
   <si>
-    <t>Age</t>
+    <t>trudnoca_po_redu</t>
   </si>
   <si>
-    <t>Gravidity</t>
+    <t>tetanus_vakcina_po_redu</t>
   </si>
   <si>
-    <t>Tetanus_vaccine</t>
+    <t>sedmica_trudnoce</t>
   </si>
   <si>
-    <t>Gestational_age</t>
+    <t>tezina</t>
   </si>
   <si>
-    <t>Weight</t>
+    <t>visina</t>
   </si>
   <si>
-    <t>Height</t>
+    <t>krvni_pritisak</t>
   </si>
   <si>
-    <t>Blood_pressure</t>
+    <t>anemija</t>
   </si>
   <si>
-    <t>Anemia</t>
+    <t>zutica</t>
   </si>
   <si>
-    <t>Jaundice</t>
+    <t>polozaj_fetusa</t>
   </si>
   <si>
-    <t>Fetal presentation</t>
+    <t>pokreti_fetusa</t>
   </si>
   <si>
-    <t>Fetal_movements</t>
+    <t>otkucaji_srca_fetusa</t>
   </si>
   <si>
-    <t>Fetal_heart_rate</t>
+    <t>albumin_urin</t>
   </si>
   <si>
-    <t>Urine_albumin</t>
+    <t>hepatitisb</t>
   </si>
   <si>
-    <t>Urine_sugar</t>
+    <t>sifillis</t>
   </si>
   <si>
-    <t>Syphilis_screening</t>
+    <t>test_urina_za_dijabetes</t>
   </si>
   <si>
-    <t>Hepatitis_B_test</t>
+    <t>rizicna_trudnoca</t>
   </si>
   <si>
-    <t>High_risk_pregnancy</t>
+    <t>ime</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1361,6 +1361,12 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <color rgb="FF202124"/>
+      <name val="Docs-Roboto"/>
+    </font>
+    <font>
+      <b/>
       <sz val="8"/>
       <color rgb="FF202124"/>
       <name val="Docs-Roboto"/>
@@ -1368,10 +1374,8 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <color rgb="FF202124"/>
+      <name val="Docs-Roboto"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1421,7 +1425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1450,7 +1454,12 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1756,58 +1765,58 @@
   <sheetData>
     <row r="1" spans="1:18" ht="30.75" customHeight="1" thickBot="1">
       <c r="A1" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="L1" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" s="11" t="s">
         <v>422</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="N1" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q1" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="O1" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="P1" t="s">
-        <v>426</v>
-      </c>
-      <c r="Q1" s="10" t="s">
+      <c r="R1" s="9" t="s">
         <v>427</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="16.5" thickBot="1">
